--- a/DATA_DANTONTAR_DANKITAR.xlsx
+++ b/DATA_DANTONTAR_DANKITAR.xlsx
@@ -250,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -421,6 +421,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,7 +865,11 @@
       <c r="E4" s="22" t="n">
         <v>2013</v>
       </c>
-      <c r="F4" s="1" t="n"/>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>92030420</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="n"/>
       <c r="H4" s="1" t="n"/>
       <c r="I4" s="1" t="n"/>
@@ -887,15 +895,27 @@
       <c r="A5" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="25" t="n"/>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>BAGUS AGUNG SUBAHENDRO, S.Tr.K.</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
           <t>DANKI TAR A</t>
         </is>
       </c>
       <c r="E5" s="26" t="n"/>
-      <c r="F5" s="1" t="n"/>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>94111168</t>
+        </is>
+      </c>
       <c r="G5" s="1" t="n"/>
       <c r="H5" s="1" t="n"/>
       <c r="I5" s="1" t="n"/>
@@ -921,15 +941,27 @@
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="28" t="n"/>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>AGUNG BUDIMAN, S.T.K., S.I.K.</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
           <t>DANKI TAR B</t>
         </is>
       </c>
       <c r="E6" s="29" t="n"/>
-      <c r="F6" s="1" t="n"/>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>92040556</t>
+        </is>
+      </c>
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
       <c r="I6" s="1" t="n"/>
@@ -973,7 +1005,11 @@
       <c r="E7" s="10" t="n">
         <v>2019</v>
       </c>
-      <c r="F7" s="1" t="n"/>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>97070941</t>
+        </is>
+      </c>
       <c r="G7" s="1" t="n"/>
       <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
@@ -1017,7 +1053,11 @@
       <c r="E8" s="10" t="n">
         <v>2016</v>
       </c>
-      <c r="F8" s="1" t="n"/>
+      <c r="F8" s="58" t="inlineStr">
+        <is>
+          <t>94011142</t>
+        </is>
+      </c>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
       <c r="I8" s="1" t="n"/>
@@ -1061,7 +1101,11 @@
       <c r="E9" s="10" t="n">
         <v>2016</v>
       </c>
-      <c r="F9" s="1" t="n"/>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>93041108</t>
+        </is>
+      </c>
       <c r="G9" s="1" t="n"/>
       <c r="H9" s="1" t="n"/>
       <c r="I9" s="1" t="n"/>
@@ -1105,7 +1149,11 @@
       <c r="E10" s="33" t="n">
         <v>2022</v>
       </c>
-      <c r="F10" s="1" t="n"/>
+      <c r="F10" s="58" t="inlineStr">
+        <is>
+          <t>98070826</t>
+        </is>
+      </c>
       <c r="G10" s="1" t="n"/>
       <c r="H10" s="1" t="n"/>
       <c r="I10" s="1" t="n"/>
@@ -1147,7 +1195,11 @@
         </is>
       </c>
       <c r="E11" s="33" t="n"/>
-      <c r="F11" s="1" t="n"/>
+      <c r="F11" s="58" t="inlineStr">
+        <is>
+          <t>93060352</t>
+        </is>
+      </c>
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
@@ -1189,7 +1241,11 @@
         </is>
       </c>
       <c r="E12" s="10" t="n"/>
-      <c r="F12" s="1" t="n"/>
+      <c r="F12" s="58" t="inlineStr">
+        <is>
+          <t>89060356</t>
+        </is>
+      </c>
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
@@ -1233,7 +1289,11 @@
       <c r="E13" s="10" t="n">
         <v>2022</v>
       </c>
-      <c r="F13" s="1" t="n"/>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>98050961</t>
+        </is>
+      </c>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
@@ -1275,7 +1335,11 @@
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="1" t="n"/>
+      <c r="F14" s="58" t="inlineStr">
+        <is>
+          <t>82020196</t>
+        </is>
+      </c>
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
@@ -1361,7 +1425,11 @@
       <c r="E16" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="F16" s="1" t="n"/>
+      <c r="F16" s="58" t="inlineStr">
+        <is>
+          <t>02021501</t>
+        </is>
+      </c>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
@@ -1405,7 +1473,11 @@
       <c r="E17" s="36" t="n">
         <v>2022</v>
       </c>
-      <c r="F17" s="1" t="n"/>
+      <c r="F17" s="58" t="inlineStr">
+        <is>
+          <t>97101003</t>
+        </is>
+      </c>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
@@ -1447,7 +1519,11 @@
         </is>
       </c>
       <c r="E18" s="36" t="n"/>
-      <c r="F18" s="1" t="n"/>
+      <c r="F18" s="58" t="inlineStr">
+        <is>
+          <t>89080457</t>
+        </is>
+      </c>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
@@ -1621,7 +1697,11 @@
       <c r="E22" s="10" t="n">
         <v>2022</v>
       </c>
-      <c r="F22" s="1" t="n"/>
+      <c r="F22" s="58" t="inlineStr">
+        <is>
+          <t>99040997</t>
+        </is>
+      </c>
       <c r="G22" s="1" t="n"/>
       <c r="H22" s="1" t="n"/>
       <c r="I22" s="1" t="n"/>
@@ -1663,7 +1743,11 @@
         </is>
       </c>
       <c r="E23" s="39" t="n"/>
-      <c r="F23" s="1" t="n"/>
+      <c r="F23" s="58" t="inlineStr">
+        <is>
+          <t>93111154</t>
+        </is>
+      </c>
       <c r="G23" s="1" t="n"/>
       <c r="H23" s="1" t="n"/>
       <c r="I23" s="1" t="n"/>
@@ -1705,7 +1789,11 @@
         </is>
       </c>
       <c r="E24" s="33" t="n"/>
-      <c r="F24" s="1" t="n"/>
+      <c r="F24" s="58" t="inlineStr">
+        <is>
+          <t>99040191</t>
+        </is>
+      </c>
       <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="n"/>
       <c r="I24" s="1" t="n"/>
@@ -29230,6 +29318,11 @@
       <c r="E7" s="10" t="n">
         <v>2016</v>
       </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>94081261</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28.5" customHeight="1" s="56">
       <c r="A8" s="6" t="n">
@@ -29253,6 +29346,11 @@
       <c r="E8" s="9" t="n">
         <v>2017</v>
       </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>92040597</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28.5" customHeight="1" s="56">
       <c r="A9" s="6" t="n">
@@ -29276,6 +29374,11 @@
       <c r="E9" s="10" t="n">
         <v>2016</v>
       </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>94041309</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28.5" customHeight="1" s="56">
       <c r="A10" s="43" t="n">
@@ -29299,6 +29402,11 @@
       <c r="E10" s="10" t="n">
         <v>2017</v>
       </c>
+      <c r="F10" s="59" t="inlineStr">
+        <is>
+          <t>95031272</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28.5" customHeight="1" s="56">
       <c r="A11" s="43" t="n">
@@ -29343,6 +29451,11 @@
         </is>
       </c>
       <c r="E12" s="10" t="n"/>
+      <c r="F12" s="59" t="inlineStr">
+        <is>
+          <t>88101015</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" s="56">
       <c r="A13" s="43" t="n">
@@ -29364,6 +29477,11 @@
         </is>
       </c>
       <c r="E13" s="10" t="n"/>
+      <c r="F13" s="59" t="inlineStr">
+        <is>
+          <t>92050091</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28.5" customHeight="1" s="56">
       <c r="A14" s="43" t="n">
@@ -29385,6 +29503,11 @@
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
+      <c r="F14" s="59" t="inlineStr">
+        <is>
+          <t>86120705</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="28.5" customHeight="1" s="56">
       <c r="A15" s="6" t="n">
@@ -29406,6 +29529,11 @@
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
+      <c r="F15" s="59" t="inlineStr">
+        <is>
+          <t>87011486</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="28.5" customHeight="1" s="56">
       <c r="A16" s="43" t="n">
@@ -29429,6 +29557,11 @@
       <c r="E16" s="10" t="n">
         <v>2022</v>
       </c>
+      <c r="F16" s="59" t="inlineStr">
+        <is>
+          <t>00111147</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28.5" customHeight="1" s="56">
       <c r="A17" s="43" t="n">
@@ -29452,6 +29585,11 @@
       <c r="E17" s="10" t="n">
         <v>2022</v>
       </c>
+      <c r="F17" s="59" t="inlineStr">
+        <is>
+          <t>00020930</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28.5" customHeight="1" s="56">
       <c r="A18" s="6" t="n">
@@ -29473,6 +29611,11 @@
         </is>
       </c>
       <c r="E18" s="10" t="n"/>
+      <c r="F18" s="59" t="inlineStr">
+        <is>
+          <t>91020176</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28.5" customHeight="1" s="56">
       <c r="A19" s="43" t="n">
@@ -29515,6 +29658,11 @@
         </is>
       </c>
       <c r="E20" s="10" t="n"/>
+      <c r="F20" s="59" t="inlineStr">
+        <is>
+          <t>87080538</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28.5" customHeight="1" s="56">
       <c r="A21" s="6" t="n">
@@ -29538,6 +29686,11 @@
       <c r="E21" s="10" t="n">
         <v>2022</v>
       </c>
+      <c r="F21" s="59" t="inlineStr">
+        <is>
+          <t>99060895</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28.5" customHeight="1" s="56">
       <c r="A22" s="43" t="n">
@@ -29559,6 +29712,11 @@
         </is>
       </c>
       <c r="E22" s="10" t="n"/>
+      <c r="F22" s="59" t="inlineStr">
+        <is>
+          <t>88051081</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28.5" customHeight="1" s="56">
       <c r="A23" s="43" t="n">
@@ -29582,6 +29740,11 @@
       <c r="E23" s="10" t="n">
         <v>2023</v>
       </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>01031201</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28.5" customHeight="1" s="56">
       <c r="A24" s="6" t="n">
@@ -29603,6 +29766,11 @@
         </is>
       </c>
       <c r="E24" s="10" t="n"/>
+      <c r="F24" s="59" t="inlineStr">
+        <is>
+          <t>92100029</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28.5" customHeight="1" s="56">
       <c r="A25" s="43" t="n">
